--- a/assets/npv/Capital Budgeting & Project Financing.xlsx
+++ b/assets/npv/Capital Budgeting & Project Financing.xlsx
@@ -1,20 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdwho\Dropbox (Personal)\Courses\Teaching\Financial Analytics\Course\4 - Capital Budgeting &amp; Project Financing\1 - Async\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdwho\Dropbox\Courses\Teaching\Financial Analytics\Course\4 - Capital Budgeting &amp; Project Financing\1 - Async\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D54FA34-133A-4228-8412-7625FC3AB278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75974B44-84E6-4AB0-94A3-C725CD457370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10876" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Investment Rules" sheetId="1" r:id="rId1"/>
     <sheet name="WACC" sheetId="2" r:id="rId2"/>
+    <sheet name="Financial Leverage" sheetId="3" r:id="rId3"/>
+    <sheet name="Changing Capital Structure" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="34">
   <si>
     <t>A project cost $100 today and pays $50 for the next three years. The cost of capital is 10%. What is the…</t>
   </si>
@@ -88,15 +90,67 @@
   </si>
   <si>
     <t>WACC</t>
+  </si>
+  <si>
+    <t>Project Cost</t>
+  </si>
+  <si>
+    <t>Project Return</t>
+  </si>
+  <si>
+    <t>Gains from Equity</t>
+  </si>
+  <si>
+    <t>Gains from Debt</t>
+  </si>
+  <si>
+    <t>Repay Debt</t>
+  </si>
+  <si>
+    <t>Debt (Borrow)</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Equity</t>
+  </si>
+  <si>
+    <t>Return of Equity</t>
+  </si>
+  <si>
+    <t>Asset beta</t>
+  </si>
+  <si>
+    <t>Equity beta</t>
+  </si>
+  <si>
+    <t>Risk-free rate</t>
+  </si>
+  <si>
+    <t>Old D/E</t>
+  </si>
+  <si>
+    <t>New D/E</t>
+  </si>
+  <si>
+    <t>Market Risk Premium</t>
+  </si>
+  <si>
+    <t>Old Equity beta</t>
+  </si>
+  <si>
+    <t>Equity Weight</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -159,7 +213,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
@@ -181,6 +235,14 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="12" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -201,6 +263,111 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB0AAC4F-1CA3-C356-FF7E-11C3A25B902F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4607720" y="178595"/>
+          <a:ext cx="4843463" cy="2707480"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>376237</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>64295</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Graphic 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA0ED78F-A3A4-6019-5C58-B33CB7418BCD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId4"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4607720" y="3036095"/>
+          <a:ext cx="4876800" cy="2743200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -467,40 +634,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.36328125" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" customWidth="1"/>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="12.6328125" style="4" customWidth="1"/>
-    <col min="9" max="9" width="14.54296875" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="12.59765625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="14.53125" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="11"/>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-    </row>
-    <row r="5" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A2" s="19"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+    </row>
+    <row r="5" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="1">
-        <v>2</v>
-      </c>
+      <c r="B5" s="1"/>
       <c r="G5" s="5" t="s">
         <v>3</v>
       </c>
@@ -511,33 +676,27 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="G6" s="4">
         <v>0</v>
       </c>
       <c r="H6" s="6">
         <v>-100</v>
       </c>
-      <c r="I6" s="7">
-        <f>H6</f>
-        <v>-100</v>
-      </c>
-      <c r="J6" t="str">
+      <c r="I6" s="7"/>
+      <c r="J6" t="e">
         <f ca="1">_xlfn.FORMULATEXT(I6)</f>
-        <v>=H6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="2">
-        <f>H6+NPV(10%,H7:H9)</f>
-        <v>24.342599549211116</v>
-      </c>
-      <c r="C7" t="str">
+      <c r="B7" s="2"/>
+      <c r="C7" t="e">
         <f ca="1">_xlfn.FORMULATEXT(B7)</f>
-        <v>=H6+NPV(10%,H7:H9)</v>
+        <v>#N/A</v>
       </c>
       <c r="G7" s="4">
         <v>1</v>
@@ -545,42 +704,33 @@
       <c r="H7" s="6">
         <v>50</v>
       </c>
-      <c r="I7" s="7">
-        <f>H7+I6</f>
-        <v>-50</v>
-      </c>
-      <c r="J7" t="str">
+      <c r="I7" s="7"/>
+      <c r="J7" t="e">
         <f t="shared" ref="J7:J9" ca="1" si="0">_xlfn.FORMULATEXT(I7)</f>
-        <v>=H7+I6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="G8" s="4">
         <v>2</v>
       </c>
       <c r="H8" s="6">
         <v>50</v>
       </c>
-      <c r="I8" s="8">
-        <f t="shared" ref="I8:I9" si="1">H8+I7</f>
-        <v>0</v>
-      </c>
-      <c r="J8" t="str">
+      <c r="I8" s="8"/>
+      <c r="J8" t="e">
         <f t="shared" ca="1" si="0"/>
-        <v>=H8+I7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="3">
-        <f>IRR(H6:H9)</f>
-        <v>0.23375192852825655</v>
-      </c>
-      <c r="C9" t="str">
+      <c r="B9" s="3"/>
+      <c r="C9" t="e">
         <f ca="1">_xlfn.FORMULATEXT(B9)</f>
-        <v>=IRR(H6:H9)</v>
+        <v>#N/A</v>
       </c>
       <c r="G9" s="4">
         <v>3</v>
@@ -588,13 +738,10 @@
       <c r="H9" s="6">
         <v>50</v>
       </c>
-      <c r="I9" s="7">
-        <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-      <c r="J9" t="str">
+      <c r="I9" s="7"/>
+      <c r="J9" t="e">
         <f t="shared" ca="1" si="0"/>
-        <v>=H9+I8</v>
+        <v>#N/A</v>
       </c>
     </row>
   </sheetData>
@@ -608,31 +755,31 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5998914-E552-4320-99AA-BBFC48E15540}">
   <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="13.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A1" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="11"/>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A2" s="19"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -640,7 +787,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -648,7 +795,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -656,7 +803,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -664,7 +811,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -672,7 +819,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -680,43 +827,34 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="10">
-        <f>B4+B5</f>
-        <v>6.0000000000000005E-2</v>
-      </c>
-      <c r="C12" t="str">
+      <c r="B12" s="10"/>
+      <c r="C12" t="e">
         <f ca="1">_xlfn.FORMULATEXT(B12)</f>
-        <v>=B4+B5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="10">
-        <f>B4+B6*B7</f>
-        <v>0.13</v>
-      </c>
-      <c r="C13" t="str">
+      <c r="B13" s="10"/>
+      <c r="C13" t="e">
         <f ca="1">_xlfn.FORMULATEXT(B13)</f>
-        <v>=B4+B6*B7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="10">
-        <f>B9*B12*(1-B8)+(1-B9)*B13</f>
-        <v>0.10095999999999999</v>
-      </c>
-      <c r="C14" t="str">
+      <c r="B14" s="10"/>
+      <c r="C14" t="e">
         <f ca="1">_xlfn.FORMULATEXT(B14)</f>
-        <v>=B9*B12*(1-B8)+(1-B9)*B13</v>
+        <v>#N/A</v>
       </c>
     </row>
   </sheetData>
@@ -725,4 +863,260 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{015BBFCE-9371-4189-8032-A3EC2B00017E}">
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="12.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.73046875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.53125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.53125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="10">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B3" s="12"/>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="13">
+        <f>B7*B2</f>
+        <v>5</v>
+      </c>
+      <c r="F3" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(E3)</f>
+        <v>=B7*B2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="13">
+        <f>B6*B2</f>
+        <v>5</v>
+      </c>
+      <c r="F4" t="str">
+        <f t="shared" ref="F4:F7" ca="1" si="0">_xlfn.FORMULATEXT(E4)</f>
+        <v>=B6*B2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="12">
+        <v>0.05</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="15">
+        <f>-B6*B5</f>
+        <v>-2.5</v>
+      </c>
+      <c r="F5" s="14" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>=-B6*B5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="11">
+        <v>50</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="13">
+        <f>SUM(E3:E5)</f>
+        <v>7.5</v>
+      </c>
+      <c r="F6" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>=SUM(E3:E5)</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="11">
+        <f>B1-B6</f>
+        <v>50</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="10">
+        <f>E6/B7</f>
+        <v>0.15</v>
+      </c>
+      <c r="F7" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>=E6/B7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B1D6C9C-4FAB-46A2-8331-DFF6E4267DB6}">
+  <dimension ref="A2:C15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="17.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.73046875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="16">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="16">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="9">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="9">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="9">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="17"/>
+      <c r="C9" t="e">
+        <f ca="1">_xlfn.FORMULATEXT(B9)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="17"/>
+      <c r="C10" t="e">
+        <f ca="1">_xlfn.FORMULATEXT(B10)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="18">
+        <f>B4+B10*B5</f>
+        <v>0.01</v>
+      </c>
+      <c r="C11" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(B11)</f>
+        <v>=B4+B10*B5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="9">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="9">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="9">
+        <f>1-B13</f>
+        <v>0.75</v>
+      </c>
+      <c r="C14" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(B14)</f>
+        <v>=1-B13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="18">
+        <f>B13*B12*(1-B6)+B14*B11</f>
+        <v>1.2749999999999999E-2</v>
+      </c>
+      <c r="C15" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(B15)</f>
+        <v>=B13*B12*(1-B6)+B14*B11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>